--- a/SGC-CKN/Excel/45b21fe1-1e82-4ee6-8fa7-f94005a0182d_Thi_công_cọc_khoan_nhồi_P2-42_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/45b21fe1-1e82-4ee6-8fa7-f94005a0182d_Thi_công_cọc_khoan_nhồi_P2-42_D800_02-04-2026.xlsx
@@ -112,7 +112,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">15:45
+    <t xml:space="preserve">15:35
 01/04/2026</t>
   </si>
   <si>
@@ -1183,13 +1183,13 @@
         <v>-5.05</v>
       </c>
       <c r="H12" s="9">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
       <c r="J12" s="8">
-        <v>6.2</v>
+        <v>9.3</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1215,16 +1215,16 @@
         <v>-5.05</v>
       </c>
       <c r="G13" s="12">
-        <v>-8.55</v>
+        <v>-8.35</v>
       </c>
       <c r="H13" s="12">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="I13" s="12">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="8">
-        <v>14</v>
+        <v>7.92</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>29</v>
@@ -1247,19 +1247,19 @@
         <v>38</v>
       </c>
       <c r="F14" s="15">
-        <v>-8.55</v>
+        <v>-8.35</v>
       </c>
       <c r="G14" s="15">
-        <v>-12.15</v>
+        <v>-17.15</v>
       </c>
       <c r="H14" s="15">
         <v>2</v>
       </c>
       <c r="I14" s="15">
-        <v>3.6</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="18">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>29</v>
@@ -1282,19 +1282,19 @@
         <v>41</v>
       </c>
       <c r="F15" s="19">
-        <v>-12.15</v>
+        <v>-17.15</v>
       </c>
       <c r="G15" s="19">
-        <v>-21.7</v>
+        <v>-22.7</v>
       </c>
       <c r="H15" s="19">
         <v>1.17</v>
       </c>
       <c r="I15" s="19">
-        <v>9.55</v>
-      </c>
-      <c r="J15" s="8">
-        <v>8.19</v>
+        <v>5.55</v>
+      </c>
+      <c r="J15" s="18">
+        <v>4.76</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>29</v>
@@ -1317,19 +1317,19 @@
         <v>44</v>
       </c>
       <c r="F16" s="22">
-        <v>-21.7</v>
+        <v>-22.7</v>
       </c>
       <c r="G16" s="22">
-        <v>-28.6</v>
+        <v>-26.6</v>
       </c>
       <c r="H16" s="22">
         <v>1</v>
       </c>
       <c r="I16" s="22">
-        <v>6.9</v>
-      </c>
-      <c r="J16" s="8">
-        <v>6.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="J16" s="18">
+        <v>3.9</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>29</v>
@@ -1352,19 +1352,19 @@
         <v>47</v>
       </c>
       <c r="F17" s="25">
-        <v>-28.6</v>
+        <v>-26.6</v>
       </c>
       <c r="G17" s="25">
-        <v>-39.7</v>
+        <v>-39.5</v>
       </c>
       <c r="H17" s="25">
         <v>2.58</v>
       </c>
       <c r="I17" s="25">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="J17" s="18">
-        <v>4.3</v>
+        <v>4.99</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>29</v>
@@ -1387,7 +1387,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="28">
-        <v>-39.7</v>
+        <v>-39.5</v>
       </c>
       <c r="G18" s="28">
         <v>-44.43</v>
@@ -1396,10 +1396,10 @@
         <v>3.17</v>
       </c>
       <c r="I18" s="28">
-        <v>4.73</v>
+        <v>4.93</v>
       </c>
       <c r="J18" s="18">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1589,13 +1589,13 @@
         <v>-5.05</v>
       </c>
       <c r="G3" s="9">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
       <c r="I3" s="8">
-        <v>6.2</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1615,16 +1615,16 @@
         <v>-5.05</v>
       </c>
       <c r="F4" s="12">
-        <v>-8.55</v>
+        <v>-8.35</v>
       </c>
       <c r="G4" s="12">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H4" s="12">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="8">
-        <v>14</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1641,19 +1641,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-8.55</v>
+        <v>-8.35</v>
       </c>
       <c r="F5" s="15">
-        <v>-12.15</v>
+        <v>-17.15</v>
       </c>
       <c r="G5" s="15">
         <v>2</v>
       </c>
       <c r="H5" s="15">
-        <v>3.6</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="18">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1670,19 +1670,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-12.15</v>
+        <v>-17.15</v>
       </c>
       <c r="F6" s="19">
-        <v>-21.7</v>
+        <v>-22.7</v>
       </c>
       <c r="G6" s="19">
         <v>1.17</v>
       </c>
       <c r="H6" s="19">
-        <v>9.55</v>
-      </c>
-      <c r="I6" s="8">
-        <v>8.19</v>
+        <v>5.55</v>
+      </c>
+      <c r="I6" s="18">
+        <v>4.76</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1699,19 +1699,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-21.7</v>
+        <v>-22.7</v>
       </c>
       <c r="F7" s="22">
-        <v>-28.6</v>
+        <v>-26.6</v>
       </c>
       <c r="G7" s="22">
         <v>1</v>
       </c>
       <c r="H7" s="22">
-        <v>6.9</v>
-      </c>
-      <c r="I7" s="8">
-        <v>6.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="I7" s="18">
+        <v>3.9</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1728,19 +1728,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-28.6</v>
+        <v>-26.6</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.7</v>
+        <v>-39.5</v>
       </c>
       <c r="G8" s="25">
         <v>2.58</v>
       </c>
       <c r="H8" s="25">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="I8" s="18">
-        <v>4.3</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1757,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.7</v>
+        <v>-39.5</v>
       </c>
       <c r="F9" s="28">
         <v>-44.43</v>
@@ -1766,10 +1766,10 @@
         <v>3.17</v>
       </c>
       <c r="H9" s="28">
-        <v>4.73</v>
+        <v>4.93</v>
       </c>
       <c r="I9" s="18">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
